--- a/Full-LC-AUTO/dist/release/Full-LC-AUTO/data inputs/jeans/Product-Description-inputs-Shopsy.xlsx
+++ b/Full-LC-AUTO/dist/release/Full-LC-AUTO/data inputs/jeans/Product-Description-inputs-Shopsy.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESHAAN\HAKUR\work--fk-tools\Full-LC-AUTO\data inputs\jeans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B0F32C8-F15F-4995-8EE9-72D78FDF12D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E89DF8-1C9C-4BE0-A40D-56B32AB3D9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,11 @@
     <sheet name="Jeans Field Guide" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="59">
   <si>
     <t>kind</t>
   </si>
@@ -87,9 +86,6 @@
     <t>Western Wear</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Clean Look</t>
   </si>
   <si>
@@ -196,6 +192,12 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>White-Baggy</t>
+  </si>
+  <si>
+    <t>WBBJ-NY-</t>
   </si>
 </sst>
 </file>
@@ -572,10 +574,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -616,7 +618,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -648,27 +650,27 @@
         <v>20</v>
       </c>
       <c r="K2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
         <v>22</v>
       </c>
-      <c r="M2" t="s">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>24</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
         <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
@@ -680,7 +682,7 @@
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
         <v>19</v>
@@ -689,27 +691,27 @@
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" t="s">
         <v>22</v>
       </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
         <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -721,7 +723,7 @@
         <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
         <v>19</v>
@@ -730,27 +732,27 @@
         <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s">
         <v>22</v>
       </c>
-      <c r="M4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
@@ -762,7 +764,7 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
@@ -771,27 +773,27 @@
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s">
         <v>22</v>
       </c>
-      <c r="M5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
         <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
@@ -803,7 +805,7 @@
         <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I6" t="s">
         <v>19</v>
@@ -812,13 +814,54 @@
         <v>20</v>
       </c>
       <c r="K6" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>57</v>
       </c>
-      <c r="L6" t="s">
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s">
         <v>22</v>
-      </c>
-      <c r="M6" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -829,174 +872,174 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>36</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
       <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
         <v>39</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>40</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>42</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>45</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>46</v>
-      </c>
-      <c r="D4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>47</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>48</v>
-      </c>
-      <c r="D5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>49</v>
       </c>
       <c r="B6" t="s">
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>52</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>53</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
